--- a/rules/CORE-000262/negative/02/data/unit-test-coreid-CG0226-negative 2.xlsx
+++ b/rules/CORE-000262/negative/02/data/unit-test-coreid-CG0226-negative 2.xlsx
@@ -65,7 +65,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none">
         <bgColor/>
@@ -79,12 +79,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -114,7 +108,7 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -122,7 +116,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -543,7 +536,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="str">
-        <v>dm.xpt</v>
+        <v>ae.xpt</v>
       </c>
       <c r="C2" s="2" t="str">
         <v>Record</v>
@@ -552,7 +545,10 @@
         <v>5</v>
       </c>
       <c r="E2" s="4" t="str">
-        <v>RFSTDTC</v>
+        <v>AESTRF</v>
+      </c>
+      <c r="F2" s="4" t="str">
+        <v>BEFORE</v>
       </c>
     </row>
     <row r="3">
@@ -560,7 +556,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="str">
-        <v>ae.xpt</v>
+        <v>dm.xpt</v>
       </c>
       <c r="C3" s="2" t="str">
         <v>Record</v>
@@ -569,10 +565,7 @@
         <v>5</v>
       </c>
       <c r="E3" s="4" t="str">
-        <v>AESTRF</v>
-      </c>
-      <c r="F3" s="4" t="str">
-        <v>BEFORE</v>
+        <v>RFSTDTC</v>
       </c>
     </row>
     <row r="4">
@@ -580,7 +573,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="str">
-        <v>dm.xpt</v>
+        <v>ae.xpt</v>
       </c>
       <c r="C4" s="2" t="str">
         <v>Record</v>
@@ -589,7 +582,10 @@
         <v>7</v>
       </c>
       <c r="E4" s="4" t="str">
-        <v>RFSTDTC</v>
+        <v>AESTRF</v>
+      </c>
+      <c r="F4" s="4" t="str">
+        <v>BEFORE</v>
       </c>
     </row>
     <row r="5">
@@ -597,7 +593,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="str">
-        <v>ae.xpt</v>
+        <v>dm.xpt</v>
       </c>
       <c r="C5" s="2" t="str">
         <v>Record</v>
@@ -606,10 +602,7 @@
         <v>7</v>
       </c>
       <c r="E5" s="4" t="str">
-        <v>AESTRF</v>
-      </c>
-      <c r="F5" s="4" t="str">
-        <v>BEFORE</v>
+        <v>RFSTDTC</v>
       </c>
     </row>
     <row r="6">
@@ -617,7 +610,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="2" t="str">
-        <v>dm.xpt</v>
+        <v>ae.xpt</v>
       </c>
       <c r="C6" s="2" t="str">
         <v>Record</v>
@@ -626,7 +619,10 @@
         <v>10</v>
       </c>
       <c r="E6" s="4" t="str">
-        <v>RFSTDTC</v>
+        <v>AESTRF</v>
+      </c>
+      <c r="F6" s="4" t="str">
+        <v>BEFORE</v>
       </c>
     </row>
     <row r="7">
@@ -634,7 +630,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="str">
-        <v>ae.xpt</v>
+        <v>dm.xpt</v>
       </c>
       <c r="C7" s="2" t="str">
         <v>Record</v>
@@ -643,10 +639,7 @@
         <v>10</v>
       </c>
       <c r="E7" s="4" t="str">
-        <v>AESTRF</v>
-      </c>
-      <c r="F7" s="4" t="str">
-        <v>BEFORE</v>
+        <v>RFSTDTC</v>
       </c>
     </row>
     <row r="8">
@@ -654,7 +647,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="str">
-        <v>dm.xpt</v>
+        <v>ae.xpt</v>
       </c>
       <c r="C8" s="2" t="str">
         <v>Record</v>
@@ -663,7 +656,10 @@
         <v>13</v>
       </c>
       <c r="E8" s="4" t="str">
-        <v>RFSTDTC</v>
+        <v>AESTRF</v>
+      </c>
+      <c r="F8" s="4" t="str">
+        <v>ONGOING</v>
       </c>
     </row>
     <row r="9">
@@ -671,7 +667,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="2" t="str">
-        <v>ae.xpt</v>
+        <v>dm.xpt</v>
       </c>
       <c r="C9" s="2" t="str">
         <v>Record</v>
@@ -680,10 +676,7 @@
         <v>13</v>
       </c>
       <c r="E9" s="4" t="str">
-        <v>AESTRF</v>
-      </c>
-      <c r="F9" s="4" t="str">
-        <v>ONGOING</v>
+        <v>RFSTDTC</v>
       </c>
     </row>
   </sheetData>
@@ -2371,7 +2364,7 @@
       <c r="AH5" s="4">
         <v>32</v>
       </c>
-      <c r="AI5" s="7" t="str">
+      <c r="AI5" s="6" t="str">
         <v>BEFORE</v>
       </c>
       <c r="AJ5" s="2" t="str">
@@ -2591,7 +2584,7 @@
       <c r="AH7" s="4">
         <v>28</v>
       </c>
-      <c r="AI7" s="7" t="str">
+      <c r="AI7" s="6" t="str">
         <v>BEFORE</v>
       </c>
       <c r="AJ7" s="2" t="str">
@@ -2921,7 +2914,7 @@
       <c r="AH10" s="4">
         <v>44</v>
       </c>
-      <c r="AI10" s="7" t="str">
+      <c r="AI10" s="6" t="str">
         <v>BEFORE</v>
       </c>
       <c r="AJ10" s="4" t="str">
@@ -3248,7 +3241,7 @@
       <c r="AH13" s="4">
         <v>178</v>
       </c>
-      <c r="AI13" s="7" t="str">
+      <c r="AI13" s="6" t="str">
         <v>ONGOING</v>
       </c>
       <c r="AJ13" s="2" t="str">
